--- a/data/trans_orig/IP07A07-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A07-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8667</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16661</t>
+          <t>17257</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17207</t>
+          <t>17327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29146</t>
+          <t>29835</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9758</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>22241</t>
+          <t>21980</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,47 +1655,47 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>19,06%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2495</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>9990</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>4,37%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,88%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5236</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2447</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>9627</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8736</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17662</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8115</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>18400</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>19313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>33175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>19745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29833</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>32631</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43856</t>
+          <t>44184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56103</t>
+          <t>55848</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>70822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,23%</t>
         </is>
       </c>
     </row>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12271</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9276</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20159</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>23110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16750</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24699</t>
+          <t>24688</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>42684</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54091</t>
+          <t>54327</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17056</t>
+          <t>17138</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10653</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24792</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17427</t>
+          <t>18168</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19077</t>
+          <t>18387</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32762</t>
+          <t>31911</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>19510</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14302</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>24226</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25971</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>40716</t>
+          <t>41090</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,89%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>15382</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15352</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21093</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>35619</t>
+          <t>36007</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,94%</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,47 +4496,47 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>21,24%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>51,47%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>9487</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>6183</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>13554</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>31,17%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>20,32%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>51,43%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>9487</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>5653</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>13775</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>18,58%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>20611</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21707</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>28081</t>
+          <t>28178</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40304</t>
+          <t>39843</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,57%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10241</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>21811</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>38654</t>
+          <t>38852</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>42711</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>53244</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>84263</t>
+          <t>84748</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>99286</t>
+          <t>99509</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>6051</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>640</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>5597</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>7628</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>5664</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>19892</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>18717</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>37732</t>
+          <t>37657</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>40199</t>
+          <t>39856</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>53548</t>
+          <t>53865</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>49279</t>
+          <t>49630</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>61745</t>
+          <t>61519</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>92961</t>
+          <t>93268</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>111519</t>
+          <t>111176</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,13%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>7480</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>14078</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>31391</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>50592</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>24197</t>
+          <t>24780</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>41851</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>60151</t>
+          <t>60137</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>86350</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>67067</t>
+          <t>68287</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>94185</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>66679</t>
+          <t>66336</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>91880</t>
+          <t>91605</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>141591</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>175819</t>
+          <t>175983</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>178312</t>
+          <t>178514</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>207167</t>
+          <t>207503</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>216336</t>
+          <t>216933</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>244543</t>
+          <t>244985</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>403622</t>
+          <t>403206</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>444268</t>
+          <t>444202</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,64%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9714</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23134</t>
+          <t>22494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6339</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>10144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12949</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>21537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>25659</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37353</t>
+          <t>37864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9593</t>
+          <t>9111</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15540</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30465</t>
+          <t>30788</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40276</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37843</t>
+          <t>37694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47372</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72318</t>
+          <t>71874</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84888</t>
+          <t>85541</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10863</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>19891</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,72%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>10355</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>18596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24493</t>
+          <t>24967</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29619</t>
+          <t>29183</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>41252</t>
+          <t>41119</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,77%</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9438</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14687</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>18,98%</t>
         </is>
       </c>
     </row>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19667</t>
+          <t>19625</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31677</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14966</t>
+          <t>14538</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23544</t>
+          <t>23631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31404</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>46111</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>8341</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4273</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12996</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10223,12 +10223,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -10286,12 +10286,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>18179</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16229</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32628</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>707</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>446</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1581</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -10855,12 +10855,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9566</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9021</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>19990</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -10968,12 +10968,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>23560</t>
+          <t>23820</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>22462</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>32546</t>
+          <t>32375</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>44103</t>
+          <t>44221</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -11203,7 +11203,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11080</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5430</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>22822</t>
+          <t>22184</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15460</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>27305</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>10057</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>20366</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11587,12 +11587,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28106</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>42928</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>22049</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>34289</t>
+          <t>34060</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>24999</t>
+          <t>25092</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>37180</t>
+          <t>36403</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>50889</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>67530</t>
+          <t>69249</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11735,12 +11735,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>61,83%</t>
         </is>
       </c>
     </row>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>584</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>15201</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16346</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>23376</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -12219,12 +12219,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>21635</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>36123</t>
+          <t>36090</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>17727</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>30917</t>
+          <t>31009</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>43546</t>
+          <t>43706</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>63241</t>
+          <t>62437</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12332,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>31894</t>
+          <t>31552</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>33575</t>
+          <t>33184</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>47456</t>
+          <t>46988</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>69829</t>
+          <t>69311</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>89845</t>
+          <t>89946</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,52%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6577</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17253</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>27529</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>42256</t>
+          <t>42182</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>63259</t>
+          <t>63601</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>73368</t>
+          <t>75284</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>103061</t>
+          <t>103683</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>74190</t>
+          <t>73687</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>100982</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>59224</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>83302</t>
+          <t>82641</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>139701</t>
+          <t>140364</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>175810</t>
+          <t>177557</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,1%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>172597</t>
+          <t>172707</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>202895</t>
+          <t>202068</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>188719</t>
+          <t>189451</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>216150</t>
+          <t>217487</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13064,12 +13064,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>370177</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>411319</t>
+          <t>409532</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentir que todo le sale mal en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de sentir que todo le sale mal, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13633,7 +13633,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12802</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1849</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20518</t>
+          <t>20463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>22858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40853</t>
+          <t>41673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,7 +14212,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>2662</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14501,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8529</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9148</t>
+          <t>9140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>11763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24050</t>
+          <t>24726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33392</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>44072</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14649,12 +14649,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44801</t>
+          <t>44789</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53670</t>
+          <t>53721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14684,12 +14684,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>82297</t>
+          <t>81907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>95679</t>
+          <t>95824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14884,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14899,7 +14899,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15012,7 +15012,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15032,7 +15032,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5698</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -15183,12 +15183,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>9848</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12878</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7740</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15268,12 +15268,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24382</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>32466</t>
+          <t>32630</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19487</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27763</t>
+          <t>27810</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15346,12 +15346,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>46168</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>58130</t>
+          <t>58774</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15381,12 +15381,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>84,49%</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15714,7 +15714,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15729,7 +15729,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11203</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>16656</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15880,12 +15880,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -15978,12 +15978,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26175</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>34927</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15993,12 +15993,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23738</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>34511</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16028,12 +16028,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>53503</t>
+          <t>53357</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>67270</t>
+          <t>66568</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -16248,7 +16248,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3114</t>
+          <t>2872</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16283,7 +16283,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9723</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>30,13%</t>
         </is>
       </c>
     </row>
@@ -16439,7 +16439,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16454,7 +16454,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -16547,12 +16547,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13301</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16562,12 +16562,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16582,12 +16582,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16597,12 +16597,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>16775</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>28357</t>
+          <t>28453</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16632,12 +16632,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -16660,12 +16660,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>7095</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16675,12 +16675,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16695,12 +16695,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11813</t>
+          <t>11546</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16710,12 +16710,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16745,12 +16745,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17093,7 +17093,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7802</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,12 +17131,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>844</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17279,12 +17279,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13659</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>17366</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>25915</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>19969</t>
+          <t>20054</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28106</t>
+          <t>27473</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>39840</t>
+          <t>39733</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>51412</t>
+          <t>50902</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17427,12 +17427,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>82,9%</t>
         </is>
       </c>
     </row>
@@ -17577,7 +17577,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17592,7 +17592,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17612,7 +17612,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17705,7 +17705,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6815</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>15637</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,38%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>17138</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>20121</t>
+          <t>20009</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>18037</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>33177</t>
+          <t>33533</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>53007</t>
+          <t>53511</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18059,12 +18059,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>38223</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>49939</t>
+          <t>50206</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -18074,12 +18074,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>83399</t>
+          <t>82443</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>100493</t>
+          <t>101730</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18109,12 +18109,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18309,7 +18309,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>16955</t>
+          <t>17188</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>12496</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>12947</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>26138</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>5061</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>34755</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18608,12 +18608,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18628,12 +18628,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>21942</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>36419</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18643,12 +18643,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>47168</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>65939</t>
+          <t>67502</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>37958</t>
+          <t>38961</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>23120</t>
+          <t>24121</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>38022</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>52830</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>71923</t>
+          <t>71888</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18791,12 +18791,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>7025</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>17723</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>15063</t>
+          <t>14960</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>21689</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>27335</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>46486</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>44103</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>34998</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>47603</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>72935</t>
+          <t>72539</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>65392</t>
+          <t>66085</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>91831</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>69426</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>95342</t>
+          <t>95045</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>142948</t>
+          <t>144112</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>179003</t>
+          <t>181989</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>205625</t>
+          <t>205433</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>235299</t>
+          <t>234217</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>214060</t>
+          <t>214285</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>243656</t>
+          <t>244691</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19438,12 +19438,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>429540</t>
+          <t>427074</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>471547</t>
+          <t>472398</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,85%</t>
         </is>
       </c>
     </row>
